--- a/Data Aksi dan Tuntutan Wilayah.xlsx
+++ b/Data Aksi dan Tuntutan Wilayah.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="71">
   <si>
     <t>NO</t>
   </si>
@@ -53,6 +53,9 @@
     <t>TUNTUTAN</t>
   </si>
   <si>
+    <t>RINGKASAN</t>
+  </si>
+  <si>
     <t>DKI Jakarta</t>
   </si>
   <si>
@@ -66,6 +69,9 @@
   </si>
   <si>
     <t>- Copot Kepala BGN Nanik S. Deyang\n- Evaluasi pengangkatan Kepala BGN</t>
+  </si>
+  <si>
+    <t>ini data ringkasan</t>
   </si>
   <si>
     <t>kementerian esdm</t>
@@ -271,18 +277,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -725,28 +731,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -870,7 +876,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -894,6 +900,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1020,8 +1029,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:H15">
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:I15">
+  <tableColumns count="9">
     <tableColumn id="1" name="NO"/>
     <tableColumn id="7" name="TANGGAL" dataDxfId="0"/>
     <tableColumn id="2" name="WILAYAH"/>
@@ -1030,6 +1039,7 @@
     <tableColumn id="8" name="Column1"/>
     <tableColumn id="5" name="KELOMPOK AKSI"/>
     <tableColumn id="6" name="TUNTUTAN"/>
+    <tableColumn id="9" name="RINGKASAN"/>
   </tableColumns>
   <tableStyleInfo name="Data Aksi dan Tuntutan Wilayah-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1270,7 +1280,9 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7"/>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="J1" s="7"/>
       <c r="K1" s="7"/>
       <c r="L1" s="7"/>
@@ -1299,24 +1311,26 @@
         <v>46188</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="5">
         <v>200</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
-      <c r="I2" s="7"/>
+      <c r="I2" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
       <c r="L2" s="7"/>
@@ -1345,24 +1359,26 @@
         <v>46188</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="5">
         <v>40</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
@@ -1391,24 +1407,26 @@
         <v>46188</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="5">
         <v>456</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
-      <c r="I4" s="7"/>
+      <c r="I4" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
@@ -1437,24 +1455,26 @@
         <v>46188</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" s="5">
         <v>1400</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
-      <c r="I5" s="7"/>
+      <c r="I5" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
@@ -1483,24 +1503,26 @@
         <v>46188</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D6" s="5">
         <v>100</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
-      <c r="I6" s="7"/>
+      <c r="I6" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
@@ -1529,24 +1551,26 @@
         <v>46188</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D7" s="5">
         <v>250</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>30</v>
+      <c r="F7" s="9" t="s">
+        <v>32</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
-      <c r="I7" s="7"/>
+      <c r="I7" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
@@ -1575,24 +1599,26 @@
         <v>46188</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8" s="5">
         <v>50</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>34</v>
+      <c r="F8" s="9" t="s">
+        <v>36</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
-      <c r="I8" s="7"/>
+      <c r="I8" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -1621,24 +1647,26 @@
         <v>46188</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D9" s="5">
         <v>168</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
-      <c r="I9" s="7"/>
+      <c r="I9" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
@@ -1667,24 +1695,26 @@
         <v>46188</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D10" s="5">
         <v>50</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
-      <c r="I10" s="7"/>
+      <c r="I10" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
@@ -1713,24 +1743,26 @@
         <v>46188</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11" s="5">
         <v>10</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
-      <c r="I11" s="7"/>
+      <c r="I11" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
@@ -1759,24 +1791,26 @@
         <v>46188</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D12" s="5">
         <v>50</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
-      <c r="I12" s="7"/>
+      <c r="I12" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
@@ -1805,24 +1839,26 @@
         <v>46188</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" s="5">
         <v>50</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
-      <c r="I13" s="7"/>
+      <c r="I13" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
@@ -1851,24 +1887,26 @@
         <v>46188</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D14" s="5">
         <v>40</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
-      <c r="I14" s="7"/>
+      <c r="I14" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
@@ -1897,24 +1935,26 @@
         <v>46188</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D15" s="5">
         <v>200</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
-      <c r="I15" s="7"/>
+      <c r="I15" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
@@ -31515,6 +31555,8 @@
     <hyperlink ref="E14" r:id="rId19" display="Polres Halmahera Selatan"/>
     <hyperlink ref="C15" r:id="rId20" display="Kalimantan Selatan"/>
     <hyperlink ref="E15" r:id="rId21" display="South Kalimantan Provincial Parliament"/>
+    <hyperlink ref="F8" r:id="rId10" display="https://maps.app.goo.gl/pn2tGs9KkbU2Y89CA"/>
+    <hyperlink ref="F7" r:id="rId9" display="https://maps.app.goo.gl/SwfUnjTWNvn7iY7j7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
